--- a/docs/modele-economique/ScanLinkPay_Modele_Economique.xlsx
+++ b/docs/modele-economique/ScanLinkPay_Modele_Economique.xlsx
@@ -13,11 +13,15 @@
     <sheet name="Scénarios" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Prévisions" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Synthèse" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Prix" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Rentabilité" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Retraits" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Sensibilité" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Dépenses" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Prix" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Rentabilité" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Retraits" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Sensibilité" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Dépenses!$A$1:$G$72</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -86,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="370">
   <si>
     <t xml:space="preserve">ScanLinkPay</t>
   </si>
@@ -121,6 +125,9 @@
     <t xml:space="preserve">Besoin de trésorerie maximal</t>
   </si>
   <si>
+    <t xml:space="preserve">Dépenses de fonctionnement — an 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paiements nécessaires pour l’objectif (par mois)</t>
   </si>
   <si>
@@ -151,6 +158,12 @@
     <t xml:space="preserve">Les 3 années côte à côte, repères clés et graphiques.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dépenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes les charges sur une page : fixes, variables, démarrage, taxes, et où va l’argent.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prix</t>
   </si>
   <si>
@@ -860,6 +873,105 @@
   </si>
   <si>
     <t xml:space="preserve">Coûts fixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dépenses — toutes les charges sur une page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dépense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moyenne / mois an 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repère graphique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coûts fixes (équipe, hébergement, fonctionnement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coûts variables (augmentent avec l’activité)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlexPaie — envoi des retraits vers Mobile Money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlexPaie — encaissements (si à notre charge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS (inscription, sécurité)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisition — nouvelles entreprises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisition — nouveaux commerçants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquisition — nouveaux clients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total des dépenses de fonctionnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrôle : égal au « Total des coûts » de la Synthèse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une seule fois, au démarrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compte Google Play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impression des premières cartes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total démarrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxes (versées à l’État, pas des coûts de fonctionnement)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVA reversée sur nos recettes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout ce qui sort, au total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonctionnement + démarrage + taxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiffre d’affaires net (rappel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dépenses de fonctionnement pour 1 $ de chiffre d’affaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répartition sur 3 ans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Famille de dépenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Équipe (développeurs, support)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hébergement et services techniques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing et acquisition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frais FlexPaie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administration (comptabilité, bureau)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total (contrôle)</t>
   </si>
   <si>
     <t xml:space="preserve">Fixer les prix des abonnements</t>
@@ -1094,7 +1206,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -1108,11 +1220,12 @@
     <numFmt numFmtId="174" formatCode="0.0\x"/>
     <numFmt numFmtId="175" formatCode="&quot;An &quot;0"/>
     <numFmt numFmtId="176" formatCode="#,##0.0;\(#,##0.0\);\-"/>
-    <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="0.000"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
+    <numFmt numFmtId="177" formatCode="0.00&quot; $&quot;"/>
+    <numFmt numFmtId="178" formatCode="0%"/>
+    <numFmt numFmtId="179" formatCode="0.000"/>
+    <numFmt numFmtId="180" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1309,6 +1422,37 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF777777"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF0B1F6B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1397,7 +1541,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="97">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1670,6 +1814,46 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1678,7 +1862,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1686,11 +1870,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="179" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1699,10 +1879,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1715,10 +1891,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1754,7 +1926,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1836,7 +2008,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF8AA64F"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF777777"/>
+      <rgbColor rgb="FF4F81BD"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF8EA2F5"/>
@@ -1853,29 +2025,29 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF777777"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFEEF2FF"/>
       <rgbColor rgb="FFDDE3FF"/>
       <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FF93A9CE"/>
       <rgbColor rgb="FFD09493"/>
-      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FF8064A2"/>
       <rgbColor rgb="FFFDE2E2"/>
       <rgbColor rgb="FF4A7EBB"/>
-      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF4BACC6"/>
       <rgbColor rgb="FF98B855"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FF9BBB59"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF725990"/>
-      <rgbColor rgb="FF93A9CE"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF0B1F6B"/>
       <rgbColor rgb="FF4299B0"/>
       <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FFBE4B48"/>
       <rgbColor rgb="FF1A3BE0"/>
       <rgbColor rgb="FF555555"/>
@@ -3016,11 +3188,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="41454000"/>
-        <c:axId val="41628348"/>
+        <c:axId val="15333427"/>
+        <c:axId val="71252392"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="41454000"/>
+        <c:axId val="15333427"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3086,7 +3258,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41628348"/>
+        <c:crossAx val="71252392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3094,7 +3266,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41628348"/>
+        <c:axId val="71252392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3170,7 +3342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41454000"/>
+        <c:crossAx val="15333427"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3989,11 +4161,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="51607509"/>
-        <c:axId val="40227343"/>
+        <c:axId val="72993027"/>
+        <c:axId val="54095511"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="51607509"/>
+        <c:axId val="72993027"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4025,7 +4197,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40227343"/>
+        <c:crossAx val="54095511"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4033,7 +4205,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40227343"/>
+        <c:axId val="54095511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4075,7 +4247,700 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51607509"/>
+        <c:crossAx val="72993027"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Où va l’argent (3 ans)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4f81bd"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:explosion val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4f81bd"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="c0504d"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9bbb59"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="8064a2"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4bacc6"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dépenses!$A$44:$A$48</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Équipe (développeurs, support)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Hébergement et services techniques</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Marketing et acquisition</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Frais FlexPaie</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Administration (comptabilité, bureau)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dépenses!$B$44:$B$48</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>59475</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6602.15296540898</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29081.0760246015</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83521.4253380303</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13725</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Dépenses de fonctionnement par an (USD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Coûts fixes"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Coûts fixes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4f81bd"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Dépenses!$J$4:$L$4</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>An 3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>An 2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>An 1</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dépenses!$J$5:$L$5</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>23724</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29655</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>37068.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Coûts variables"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Coûts variables</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="c0504d"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Dépenses!$J$4:$L$4</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>An 3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>An 2</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>An 1</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dépenses!$J$6:$L$6</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10435.2634645016</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31131.607474793</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60390.0333887461</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="58348660"/>
+        <c:axId val="32771736"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="58348660"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="32771736"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="32771736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="\$#,##0;&quot;($&quot;#,##0\);\-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="58348660"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4180,6 +5045,71 @@
       <xdr:xfrm>
         <a:off x="8317080" y="6781680"/>
         <a:ext cx="5759640" cy="2879640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>520920</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>79200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5779800" y="7924680"/>
+        <a:ext cx="4679640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>78120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1037160</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>79200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="9829800"/>
+        <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4373,7 +5303,7 @@
     <tabColor rgb="FF0B1F6B"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -4493,159 +5423,176 @@
         <v>11</v>
       </c>
       <c r="C17" s="9" t="n">
+        <f aca="false">Dépenses!B23</f>
+        <v>34159.2634645016</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="9" t="n">
         <f aca="false">Rentabilité!B23</f>
         <v>237815.823174301</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>31</v>
+      <c r="B30" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
-        <v>32</v>
+      <c r="B31" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="15" t="s">
-        <v>34</v>
+      <c r="B32" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="7" t="s">
-        <v>36</v>
+      <c r="B33" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="13" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C34" s="13" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -4654,11 +5601,292 @@
     <hyperlink ref="B21" r:id="rId2" location="'Scénarios'!A1" display="Scénarios"/>
     <hyperlink ref="B22" r:id="rId3" location="'Prévisions'!A1" display="Prévisions"/>
     <hyperlink ref="B23" r:id="rId4" location="'Synthèse'!A1" display="Synthèse"/>
-    <hyperlink ref="B24" r:id="rId5" location="'Prix'!A1" display="Prix"/>
-    <hyperlink ref="B25" r:id="rId6" location="'Rentabilité'!A1" display="Rentabilité"/>
-    <hyperlink ref="B26" r:id="rId7" location="'Retraits'!A1" display="Retraits"/>
-    <hyperlink ref="B27" r:id="rId8" location="'Sensibilité'!A1" display="Sensibilité"/>
+    <hyperlink ref="B24" r:id="rId5" location="'Dépenses'!A1" display="Dépenses"/>
+    <hyperlink ref="B25" r:id="rId6" location="'Prix'!A1" display="Prix"/>
+    <hyperlink ref="B26" r:id="rId7" location="'Rentabilité'!A1" display="Rentabilité"/>
+    <hyperlink ref="B27" r:id="rId8" location="'Retraits'!A1" display="Retraits"/>
+    <hyperlink ref="B28" r:id="rId9" location="'Sensibilité'!A1" display="Sensibilité"/>
   </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF8EA2F5"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="B4" s="70" t="n">
+        <f aca="false">INDEX(Prévisions!$C$55:$AL$55,12)</f>
+        <v>-228.255271613358</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B5" s="70" t="n">
+        <f aca="false">INDEX(Prévisions!$C$21:$AL$21,12)+INDEX(Prévisions!$C$22:$AL$22,12)+INDEX(Prévisions!$C$27:$AL$27,12)</f>
+        <v>104412.27435579</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="36" t="n">
+        <f aca="false">Hypothèses!$B$16</f>
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="B7" s="86" t="n">
+        <f aca="false">Hypothèses!$B$18*(Hypothèses!$B$19/Prix!$B$4-Hypothèses!$B$20)</f>
+        <v>-0.00682758620689655</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="B9" s="96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="96" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D9" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B10" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A10/Prix!$B$4+$B$7)</f>
+        <v>-1672.02499632617</v>
+      </c>
+      <c r="C10" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A10/Prix!$B$4+$B$7)</f>
+        <v>-1625.21949402875</v>
+      </c>
+      <c r="D10" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A10/Prix!$B$4+$B$7)</f>
+        <v>-1578.41399173133</v>
+      </c>
+      <c r="E10" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A10/Prix!$B$4+$B$7)</f>
+        <v>-1484.80298713648</v>
+      </c>
+      <c r="F10" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A10/Prix!$B$4+$B$7)</f>
+        <v>-1391.19198254163</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A10/Prix!$B$4+$B$7)</f>
+        <v>-1203.96997335194</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="95" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="B11" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A11/Prix!$B$4+$B$7)</f>
+        <v>-1446.99854297318</v>
+      </c>
+      <c r="C11" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A11/Prix!$B$4+$B$7)</f>
+        <v>-1287.67981399926</v>
+      </c>
+      <c r="D11" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A11/Prix!$B$4+$B$7)</f>
+        <v>-1128.36108502534</v>
+      </c>
+      <c r="E11" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A11/Prix!$B$4+$B$7)</f>
+        <v>-809.723627077496</v>
+      </c>
+      <c r="F11" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A11/Prix!$B$4+$B$7)</f>
+        <v>-491.086169129656</v>
+      </c>
+      <c r="G11" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A11/Prix!$B$4+$B$7)</f>
+        <v>146.188746766026</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="95" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B12" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A12/Prix!$B$4+$B$7)</f>
+        <v>-1221.97208962018</v>
+      </c>
+      <c r="C12" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A12/Prix!$B$4+$B$7)</f>
+        <v>-950.140133969765</v>
+      </c>
+      <c r="D12" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A12/Prix!$B$4+$B$7)</f>
+        <v>-678.308178319347</v>
+      </c>
+      <c r="E12" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A12/Prix!$B$4+$B$7)</f>
+        <v>-134.644267018512</v>
+      </c>
+      <c r="F12" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A12/Prix!$B$4+$B$7)</f>
+        <v>409.019644282324</v>
+      </c>
+      <c r="G12" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A12/Prix!$B$4+$B$7)</f>
+        <v>1496.34746688399</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="95" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="B13" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A13/Prix!$B$4+$B$7)</f>
+        <v>-996.945636267188</v>
+      </c>
+      <c r="C13" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A13/Prix!$B$4+$B$7)</f>
+        <v>-612.600453940273</v>
+      </c>
+      <c r="D13" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A13/Prix!$B$4+$B$7)</f>
+        <v>-228.255271613358</v>
+      </c>
+      <c r="E13" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A13/Prix!$B$4+$B$7)</f>
+        <v>540.435093040472</v>
+      </c>
+      <c r="F13" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A13/Prix!$B$4+$B$7)</f>
+        <v>1309.1254576943</v>
+      </c>
+      <c r="G13" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A13/Prix!$B$4+$B$7)</f>
+        <v>2846.50618700196</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="95" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B14" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A14/Prix!$B$4+$B$7)</f>
+        <v>-771.919182914193</v>
+      </c>
+      <c r="C14" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A14/Prix!$B$4+$B$7)</f>
+        <v>-275.060773910781</v>
+      </c>
+      <c r="D14" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A14/Prix!$B$4+$B$7)</f>
+        <v>221.797635092631</v>
+      </c>
+      <c r="E14" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A14/Prix!$B$4+$B$7)</f>
+        <v>1215.51445309946</v>
+      </c>
+      <c r="F14" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A14/Prix!$B$4+$B$7)</f>
+        <v>2209.23127110628</v>
+      </c>
+      <c r="G14" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A14/Prix!$B$4+$B$7)</f>
+        <v>4196.66490711993</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="95" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="B15" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A15/Prix!$B$4+$B$7)</f>
+        <v>-546.892729561198</v>
+      </c>
+      <c r="C15" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A15/Prix!$B$4+$B$7)</f>
+        <v>62.4789061187116</v>
+      </c>
+      <c r="D15" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A15/Prix!$B$4+$B$7)</f>
+        <v>671.850541798621</v>
+      </c>
+      <c r="E15" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A15/Prix!$B$4+$B$7)</f>
+        <v>1890.59381315844</v>
+      </c>
+      <c r="F15" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A15/Prix!$B$4+$B$7)</f>
+        <v>3109.33708451826</v>
+      </c>
+      <c r="G15" s="71" t="n">
+        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A15/Prix!$B$4+$B$7)</f>
+        <v>5546.8236272379</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B10:G15">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4688,17 +5916,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -4706,14 +5934,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4721,70 +5949,70 @@
         <v>5</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>2850</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B9" s="26" t="n">
         <v>1.27</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B10" s="27" t="n">
         <v>0.16</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B11" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B12" s="27" t="n">
         <v>0.3</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -4792,107 +6020,107 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B16" s="29" t="n">
         <v>0.025</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B17" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B18" s="27" t="n">
         <v>0.6</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B19" s="29" t="n">
         <v>0.01</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B20" s="30" t="n">
         <v>0.02</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B21" s="30" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B22" s="31" t="n">
         <v>30</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B23" s="31" t="n">
         <v>20</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -4900,85 +6128,85 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C26" s="21"/>
       <c r="D26" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B27" s="32" t="n">
         <v>15</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B28" s="24" t="n">
         <v>30</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B29" s="32" t="n">
         <v>10</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B30" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B31" s="27" t="n">
         <v>0.3</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B32" s="33" t="n">
         <v>5000</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -4986,44 +6214,44 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="34" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="35" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B38" s="24" t="n">
         <v>1</v>
@@ -5044,7 +6272,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B39" s="24" t="n">
         <v>6</v>
@@ -5065,7 +6293,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B40" s="24" t="n">
         <v>12</v>
@@ -5086,7 +6314,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="35" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B41" s="24" t="n">
         <v>18</v>
@@ -5107,12 +6335,12 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
@@ -5120,52 +6348,52 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B46" s="31" t="n">
         <v>32</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B47" s="31" t="n">
         <v>25</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B48" s="31" t="n">
         <v>10</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B49" s="31" t="n">
         <v>10</v>
@@ -5174,62 +6402,62 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B50" s="31" t="n">
         <v>1000</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B51" s="31" t="n">
         <v>300</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B52" s="31" t="n">
         <v>300</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B53" s="31" t="n">
         <v>150</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B54" s="31" t="n">
         <v>150</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="38" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B55" s="39" t="n">
         <f aca="false">SUM($B$46,$B$47,$B$48,$B$49,$B$50,$B$51,$B$52,$B$53,$B$54)</f>
@@ -5238,18 +6466,18 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B56" s="27" t="n">
         <v>0.25</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -5257,85 +6485,85 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C59" s="21"/>
       <c r="D59" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B60" s="40" t="n">
         <v>4</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B61" s="40" t="n">
         <v>0.03</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B62" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B63" s="31" t="n">
         <v>15</v>
       </c>
       <c r="D63" s="25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B64" s="31" t="n">
         <v>3</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B65" s="40" t="n">
         <v>0.3</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
@@ -5343,63 +6571,63 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C68" s="21"/>
       <c r="D68" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B69" s="31" t="n">
         <v>25</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B70" s="31" t="n">
         <v>500</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B71" s="31" t="n">
         <v>200</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B72" s="31" t="n">
         <v>300</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="38" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B73" s="39" t="n">
         <f aca="false">SUM($B$69:$B$72)</f>
@@ -5408,7 +6636,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -5416,25 +6644,25 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C76" s="21"/>
       <c r="D76" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B77" s="41" t="n">
         <v>1000</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5471,37 +6699,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>3</v>
@@ -5517,12 +6745,12 @@
         <v>5</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B6" s="24" t="n">
         <v>5</v>
@@ -5541,7 +6769,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>100</v>
@@ -5560,7 +6788,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>1</v>
@@ -5579,7 +6807,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>5</v>
@@ -5598,7 +6826,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B10" s="24" t="n">
         <v>80</v>
@@ -5617,7 +6845,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B11" s="27" t="n">
         <v>0.04</v>
@@ -5633,12 +6861,12 @@
         <v>0.08</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B12" s="27" t="n">
         <v>0.02</v>
@@ -5657,7 +6885,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B13" s="27" t="n">
         <v>0.05</v>
@@ -5673,12 +6901,12 @@
         <v>0.03</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" s="27" t="n">
         <v>0.08</v>
@@ -5697,7 +6925,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B15" s="27" t="n">
         <v>0.4</v>
@@ -5716,7 +6944,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B16" s="31" t="n">
         <v>100</v>
@@ -5732,12 +6960,12 @@
         <v>300</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B17" s="31" t="n">
         <v>300</v>
@@ -5753,12 +6981,12 @@
         <v>800</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B18" s="27" t="n">
         <v>0.01</v>
@@ -5777,7 +7005,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B19" s="27" t="n">
         <v>0.08</v>
@@ -5796,7 +7024,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B20" s="27" t="n">
         <v>0.4</v>
@@ -5815,7 +7043,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>4</v>
@@ -5834,7 +7062,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B22" s="31" t="n">
         <v>150</v>
@@ -5853,7 +7081,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B23" s="27" t="n">
         <v>0.25</v>
@@ -5869,12 +7097,12 @@
         <v>0.4</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B24" s="45" t="n">
         <v>0.5</v>
@@ -5890,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -5920,17 +7148,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="38" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C4" s="47" t="n">
         <v>1</v>
@@ -6043,7 +7271,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C5" s="48" t="n">
         <f aca="false">INT((C4-1)/12)+1</f>
@@ -6192,7 +7420,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -6234,10 +7462,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C8" s="50" t="n">
         <f aca="false">1</f>
@@ -6386,10 +7614,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C9" s="51" t="n">
         <f aca="false">Scénarios!$E$8*C8</f>
@@ -6538,10 +7766,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="38" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10" s="52" t="n">
         <f aca="false">Scénarios!$E$5*(1-Scénarios!$E$13)+C9</f>
@@ -6690,10 +7918,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C11" s="51" t="n">
         <f aca="false">C10*Scénarios!$E$15</f>
@@ -6842,10 +8070,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="49" t="s">
         <v>191</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>188</v>
       </c>
       <c r="C12" s="51" t="n">
         <f aca="false">Scénarios!$E$9*C8</f>
@@ -6994,10 +8222,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="38" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C13" s="52" t="n">
         <f aca="false">Scénarios!$E$6*(1-Scénarios!$E$13)+C12</f>
@@ -7146,10 +8374,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C14" s="51" t="n">
         <f aca="false">Scénarios!$E$10*C8</f>
@@ -7298,10 +8526,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C15" s="53" t="n">
         <f aca="false">Scénarios!$E$7*(1-Scénarios!$E$14)+C14</f>
@@ -7450,10 +8678,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C16" s="51" t="n">
         <f aca="false">C10*Scénarios!$E$19</f>
@@ -7602,10 +8830,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C17" s="51" t="n">
         <f aca="false">C16*Scénarios!$E$20</f>
@@ -7754,10 +8982,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="54" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C18" s="56" t="n">
         <f aca="false">C10+C13+C15</f>
@@ -7906,7 +9134,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -7948,10 +9176,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C21" s="57" t="n">
         <f aca="false">C13*Scénarios!$E$16+C10*Scénarios!$E$17</f>
@@ -8100,10 +9328,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C22" s="57" t="n">
         <f aca="false">C17*Scénarios!$E$21*Scénarios!$E$22*Scénarios!$E$23</f>
@@ -8256,7 +9484,7 @@
         <v>API — HotelSaver (abonnements des hôtels + acomptes des clients)</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C23" s="57" t="n">
         <f aca="false">IF(AND(Hypothèses!$B$38&gt;0,C$4&gt;=Hypothèses!$B$38),Hypothèses!$C$38*(1+Hypothèses!$E$38)^(C$4-Hypothèses!$B$38)*Hypothèses!$D$38*Scénarios!$E$24,0)</f>
@@ -8409,7 +9637,7 @@
         <v>API — Application partenaire 2</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C24" s="57" t="n">
         <f aca="false">IF(AND(Hypothèses!$B$39&gt;0,C$4&gt;=Hypothèses!$B$39),Hypothèses!$C$39*(1+Hypothèses!$E$39)^(C$4-Hypothèses!$B$39)*Hypothèses!$D$39*Scénarios!$E$24,0)</f>
@@ -8562,7 +9790,7 @@
         <v>API — Application partenaire 3</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C25" s="57" t="n">
         <f aca="false">IF(AND(Hypothèses!$B$40&gt;0,C$4&gt;=Hypothèses!$B$40),Hypothèses!$C$40*(1+Hypothèses!$E$40)^(C$4-Hypothèses!$B$40)*Hypothèses!$D$40*Scénarios!$E$24,0)</f>
@@ -8715,7 +9943,7 @@
         <v>API — Application partenaire 4</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C26" s="57" t="n">
         <f aca="false">IF(AND(Hypothèses!$B$41&gt;0,C$4&gt;=Hypothèses!$B$41),Hypothèses!$C$41*(1+Hypothèses!$E$41)^(C$4-Hypothèses!$B$41)*Hypothèses!$D$41*Scénarios!$E$24,0)</f>
@@ -8864,10 +10092,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C27" s="58" t="n">
         <f aca="false">SUM(C23:C26)</f>
@@ -9016,10 +10244,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="49" t="s">
         <v>203</v>
-      </c>
-      <c r="B28" s="49" t="s">
-        <v>200</v>
       </c>
       <c r="C28" s="57" t="n">
         <f aca="false">(C21+C22)*Hypothèses!$B$18</f>
@@ -9168,10 +10396,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C29" s="57" t="n">
         <f aca="false">C15*Hypothèses!$B$22</f>
@@ -9320,10 +10548,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="54" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B30" s="55" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C30" s="39" t="n">
         <f aca="false">C21+C22+C27+C29</f>
@@ -9472,7 +10700,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -9514,10 +10742,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C33" s="57" t="n">
         <f aca="false">C21*Hypothèses!$B$16</f>
@@ -9666,10 +10894,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C34" s="57" t="n">
         <f aca="false">C22*Hypothèses!$B$16</f>
@@ -9818,10 +11046,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C35" s="57" t="n">
         <f aca="false">C23*Hypothèses!$F$38+C24*Hypothèses!$F$39+C25*Hypothèses!$F$40+C26*Hypothèses!$F$41</f>
@@ -9970,10 +11198,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C36" s="57" t="n">
         <f aca="false">C28*Hypothèses!$B$19</f>
@@ -10122,10 +11350,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C37" s="57" t="n">
         <f aca="false">C29*Hypothèses!$B$21</f>
@@ -10274,10 +11502,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C38" s="57" t="n">
         <f aca="false">C11*Hypothèses!$B$27</f>
@@ -10426,10 +11654,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C39" s="57" t="n">
         <f aca="false">C17*Hypothèses!$B$29*((1-Hypothèses!$B$31)+Hypothèses!$B$31*(12-Hypothèses!$B$30)/12)</f>
@@ -10578,10 +11806,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C40" s="57" t="n">
         <f aca="false">C15*Scénarios!$E$18*Hypothèses!$B$32/Hypothèses!$B$8</f>
@@ -10730,10 +11958,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="54" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C41" s="39" t="n">
         <f aca="false">SUM(C33:C40)</f>
@@ -10882,10 +12110,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C42" s="57" t="n">
         <f aca="false">C41-C41/(1+Hypothèses!$B$10*Hypothèses!$B$11)</f>
@@ -11034,10 +12262,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="54" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C43" s="39" t="n">
         <f aca="false">C41-C42</f>
@@ -11186,7 +12414,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -11228,10 +12456,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C46" s="57" t="n">
         <f aca="false">C28*Hypothèses!$B$20</f>
@@ -11380,10 +12608,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C47" s="57" t="n">
         <f aca="false">(C21+C22+C27)*Hypothèses!$B$17</f>
@@ -11532,10 +12760,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C48" s="57" t="n">
         <f aca="false">C18/1000*Hypothèses!$B$60</f>
@@ -11684,10 +12912,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C49" s="57" t="n">
         <f aca="false">(C9+C12+C14)*Hypothèses!$B$62*Hypothèses!$B$61</f>
@@ -11836,10 +13064,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C50" s="57" t="n">
         <f aca="false">C9*Hypothèses!$B$63+C12*Hypothèses!$B$64+C14*Hypothèses!$B$65</f>
@@ -11988,10 +13216,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C51" s="57" t="n">
         <f aca="false">Hypothèses!$B$55*(1+Hypothèses!$B$56)^(C$5-1)</f>
@@ -12140,10 +13368,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="54" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C52" s="39" t="n">
         <f aca="false">SUM(C46:C51)</f>
@@ -12292,7 +13520,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -12334,10 +13562,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="54" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C55" s="39" t="n">
         <f aca="false">C43-C52</f>
@@ -12486,10 +13714,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C56" s="57" t="n">
         <f aca="false">MAX(0,C55)*Hypothèses!$B$12</f>
@@ -12638,10 +13866,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="54" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C57" s="39" t="n">
         <f aca="false">C55-C56</f>
@@ -12790,10 +14018,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="38" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B58" s="49" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C58" s="58" t="n">
         <f aca="false">-Hypothèses!$B$73+C57</f>
@@ -12942,10 +14170,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B59" s="49" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C59" s="59" t="n">
         <f aca="false">IF(C43=0,0,C57/C43)</f>
@@ -13094,7 +14322,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B60" s="49"/>
       <c r="C60" s="60" t="n">
@@ -13244,7 +14472,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B61" s="49"/>
       <c r="C61" s="60" t="n">
@@ -13394,7 +14622,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B62" s="49"/>
       <c r="C62" s="60" t="n">
@@ -13595,7 +14823,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13606,28 +14834,28 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G4" s="61" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H4" s="62"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -13643,7 +14871,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B6" s="64" t="n">
         <f aca="false">INDEX(Prévisions!$C$10:$AL$10,12)</f>
@@ -13662,7 +14890,7 @@
         <v>241.981780203308</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="H6" s="63" t="str">
         <f aca="false">IF(MIN(Prévisions!$C$61:$AL$61)=999,"Pas en 3 ans","Mois "&amp;MIN(Prévisions!$C$61:$AL$61))</f>
@@ -13671,7 +14899,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B7" s="64" t="n">
         <f aca="false">INDEX(Prévisions!$C$13:$AL$13,12)</f>
@@ -13699,7 +14927,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B8" s="64" t="n">
         <f aca="false">INDEX(Prévisions!$C$15:$AL$15,12)</f>
@@ -13718,7 +14946,7 @@
         <v>13159.3987550997</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H8" s="65" t="n">
         <f aca="false">INDEX(Prévisions!$C$57:$AL$57,36)</f>
@@ -13727,7 +14955,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B9" s="64" t="n">
         <f aca="false">INDEX(Prévisions!$C$17:$AL$17,12)</f>
@@ -13746,7 +14974,7 @@
         <v>21.7783602182977</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H9" s="65" t="n">
         <f aca="false">INDEX(Prévisions!$C$58:$AL$58,36)</f>
@@ -13755,7 +14983,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G10" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H10" s="66" t="n">
         <f aca="false">IF(D24=0,0,(D21+D22+D23)/(1+Hypothèses!$B$10*Hypothèses!$B$11)/D24)</f>
@@ -13764,14 +14992,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="G11" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H11" s="66" t="n">
         <f aca="false">IF(D24=0,0,D18/(1+Hypothèses!$B$10*Hypothèses!$B$11)/D24)</f>
@@ -13780,7 +15008,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B12" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$30:$AL$30)</f>
@@ -13801,7 +15029,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B13" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$27:$AL$27)</f>
@@ -13822,7 +15050,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -13831,7 +15059,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B16" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$33:$AL$33)</f>
@@ -13852,7 +15080,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B17" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$34:$AL$34)</f>
@@ -13873,7 +15101,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B18" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$35:$AL$35)</f>
@@ -13894,7 +15122,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B19" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$36:$AL$36)</f>
@@ -13915,7 +15143,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B20" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$37:$AL$37)</f>
@@ -13936,7 +15164,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B21" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$38:$AL$38)</f>
@@ -13957,7 +15185,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B22" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$39:$AL$39)</f>
@@ -13978,7 +15206,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B23" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$40:$AL$40)</f>
@@ -13999,7 +15227,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="54" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B24" s="39" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$43:$AL$43)</f>
@@ -14020,7 +15248,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -14029,7 +15257,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B27" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$46:$AL$46)</f>
@@ -14050,7 +15278,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B28" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$50:$AL$50)</f>
@@ -14071,7 +15299,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B29" s="67" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$51:$AL$51)</f>
@@ -14092,7 +15320,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="54" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B30" s="39" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$52:$AL$52)</f>
@@ -14113,7 +15341,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="54" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B31" s="39" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$55:$AL$55)</f>
@@ -14134,7 +15362,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="54" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B32" s="39" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$57:$AL$57)</f>
@@ -14155,7 +15383,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="38" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B33" s="59" t="n">
         <f aca="false">IF(B24=0,0,B32/B24)</f>
@@ -14199,6 +15427,906 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF0B1F6B"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:L49"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="str">
+        <f aca="false">"Scénario : "&amp;Hypothèses!$B$7&amp;" · USD · coûts fixes augmentés de "&amp;TEXT(Hypothèses!$B$56,"0%")&amp;" par an (ans 2 et 3)"</f>
+        <v>Scénario : Réaliste · USD · coûts fixes augmentés de 25% par an (ans 2 et 3)</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="I4" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="J4" s="68" t="str">
+        <f aca="false">B4</f>
+        <v>An 1</v>
+      </c>
+      <c r="K4" s="68" t="str">
+        <f aca="false">C4</f>
+        <v>An 2</v>
+      </c>
+      <c r="L4" s="68" t="str">
+        <f aca="false">D4</f>
+        <v>An 3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="I5" s="68" t="s">
+        <v>260</v>
+      </c>
+      <c r="J5" s="69" t="n">
+        <f aca="false">SUM(B6:B14)</f>
+        <v>23724</v>
+      </c>
+      <c r="K5" s="69" t="n">
+        <f aca="false">SUM(C6:C14)</f>
+        <v>29655</v>
+      </c>
+      <c r="L5" s="69" t="n">
+        <f aca="false">SUM(D6:D14)</f>
+        <v>37068.75</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="70" t="n">
+        <f aca="false">Hypothèses!$B$46*12*(1+Hypothèses!$B$56)^0</f>
+        <v>384</v>
+      </c>
+      <c r="C6" s="70" t="n">
+        <f aca="false">Hypothèses!$B$46*12*(1+Hypothèses!$B$56)^1</f>
+        <v>480</v>
+      </c>
+      <c r="D6" s="70" t="n">
+        <f aca="false">Hypothèses!$B$46*12*(1+Hypothèses!$B$56)^2</f>
+        <v>600</v>
+      </c>
+      <c r="E6" s="71" t="n">
+        <f aca="false">SUM(B6:D6)</f>
+        <v>1464</v>
+      </c>
+      <c r="F6" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E6/$E$23)</f>
+        <v>0.00760896354151574</v>
+      </c>
+      <c r="G6" s="71" t="n">
+        <f aca="false">B6/12</f>
+        <v>32</v>
+      </c>
+      <c r="I6" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="J6" s="69" t="n">
+        <f aca="false">SUM(B16:B22)</f>
+        <v>10435.2634645016</v>
+      </c>
+      <c r="K6" s="69" t="n">
+        <f aca="false">SUM(C16:C22)</f>
+        <v>31131.607474793</v>
+      </c>
+      <c r="L6" s="69" t="n">
+        <f aca="false">SUM(D16:D22)</f>
+        <v>60390.0333887461</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="70" t="n">
+        <f aca="false">Hypothèses!$B$47*12*(1+Hypothèses!$B$56)^0</f>
+        <v>300</v>
+      </c>
+      <c r="C7" s="70" t="n">
+        <f aca="false">Hypothèses!$B$47*12*(1+Hypothèses!$B$56)^1</f>
+        <v>375</v>
+      </c>
+      <c r="D7" s="70" t="n">
+        <f aca="false">Hypothèses!$B$47*12*(1+Hypothèses!$B$56)^2</f>
+        <v>468.75</v>
+      </c>
+      <c r="E7" s="71" t="n">
+        <f aca="false">SUM(B7:D7)</f>
+        <v>1143.75</v>
+      </c>
+      <c r="F7" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E7/$E$23)</f>
+        <v>0.00594450276680917</v>
+      </c>
+      <c r="G7" s="71" t="n">
+        <f aca="false">B7/12</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="70" t="n">
+        <f aca="false">Hypothèses!$B$48*12*(1+Hypothèses!$B$56)^0</f>
+        <v>120</v>
+      </c>
+      <c r="C8" s="70" t="n">
+        <f aca="false">Hypothèses!$B$48*12*(1+Hypothèses!$B$56)^1</f>
+        <v>150</v>
+      </c>
+      <c r="D8" s="70" t="n">
+        <f aca="false">Hypothèses!$B$48*12*(1+Hypothèses!$B$56)^2</f>
+        <v>187.5</v>
+      </c>
+      <c r="E8" s="71" t="n">
+        <f aca="false">SUM(B8:D8)</f>
+        <v>457.5</v>
+      </c>
+      <c r="F8" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E8/$E$23)</f>
+        <v>0.00237780110672367</v>
+      </c>
+      <c r="G8" s="71" t="n">
+        <f aca="false">B8/12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="70" t="n">
+        <f aca="false">Hypothèses!$B$49*12*(1+Hypothèses!$B$56)^0</f>
+        <v>120</v>
+      </c>
+      <c r="C9" s="70" t="n">
+        <f aca="false">Hypothèses!$B$49*12*(1+Hypothèses!$B$56)^1</f>
+        <v>150</v>
+      </c>
+      <c r="D9" s="70" t="n">
+        <f aca="false">Hypothèses!$B$49*12*(1+Hypothèses!$B$56)^2</f>
+        <v>187.5</v>
+      </c>
+      <c r="E9" s="71" t="n">
+        <f aca="false">SUM(B9:D9)</f>
+        <v>457.5</v>
+      </c>
+      <c r="F9" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E9/$E$23)</f>
+        <v>0.00237780110672367</v>
+      </c>
+      <c r="G9" s="71" t="n">
+        <f aca="false">B9/12</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="70" t="n">
+        <f aca="false">Hypothèses!$B$50*12*(1+Hypothèses!$B$56)^0</f>
+        <v>12000</v>
+      </c>
+      <c r="C10" s="70" t="n">
+        <f aca="false">Hypothèses!$B$50*12*(1+Hypothèses!$B$56)^1</f>
+        <v>15000</v>
+      </c>
+      <c r="D10" s="70" t="n">
+        <f aca="false">Hypothèses!$B$50*12*(1+Hypothèses!$B$56)^2</f>
+        <v>18750</v>
+      </c>
+      <c r="E10" s="71" t="n">
+        <f aca="false">SUM(B10:D10)</f>
+        <v>45750</v>
+      </c>
+      <c r="F10" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E10/$E$23)</f>
+        <v>0.237780110672367</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <f aca="false">B10/12</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="70" t="n">
+        <f aca="false">Hypothèses!$B$51*12*(1+Hypothèses!$B$56)^0</f>
+        <v>3600</v>
+      </c>
+      <c r="C11" s="70" t="n">
+        <f aca="false">Hypothèses!$B$51*12*(1+Hypothèses!$B$56)^1</f>
+        <v>4500</v>
+      </c>
+      <c r="D11" s="70" t="n">
+        <f aca="false">Hypothèses!$B$51*12*(1+Hypothèses!$B$56)^2</f>
+        <v>5625</v>
+      </c>
+      <c r="E11" s="71" t="n">
+        <f aca="false">SUM(B11:D11)</f>
+        <v>13725</v>
+      </c>
+      <c r="F11" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E11/$E$23)</f>
+        <v>0.07133403320171</v>
+      </c>
+      <c r="G11" s="71" t="n">
+        <f aca="false">B11/12</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="70" t="n">
+        <f aca="false">Hypothèses!$B$52*12*(1+Hypothèses!$B$56)^0</f>
+        <v>3600</v>
+      </c>
+      <c r="C12" s="70" t="n">
+        <f aca="false">Hypothèses!$B$52*12*(1+Hypothèses!$B$56)^1</f>
+        <v>4500</v>
+      </c>
+      <c r="D12" s="70" t="n">
+        <f aca="false">Hypothèses!$B$52*12*(1+Hypothèses!$B$56)^2</f>
+        <v>5625</v>
+      </c>
+      <c r="E12" s="71" t="n">
+        <f aca="false">SUM(B12:D12)</f>
+        <v>13725</v>
+      </c>
+      <c r="F12" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E12/$E$23)</f>
+        <v>0.07133403320171</v>
+      </c>
+      <c r="G12" s="71" t="n">
+        <f aca="false">B12/12</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="70" t="n">
+        <f aca="false">Hypothèses!$B$53*12*(1+Hypothèses!$B$56)^0</f>
+        <v>1800</v>
+      </c>
+      <c r="C13" s="70" t="n">
+        <f aca="false">Hypothèses!$B$53*12*(1+Hypothèses!$B$56)^1</f>
+        <v>2250</v>
+      </c>
+      <c r="D13" s="70" t="n">
+        <f aca="false">Hypothèses!$B$53*12*(1+Hypothèses!$B$56)^2</f>
+        <v>2812.5</v>
+      </c>
+      <c r="E13" s="71" t="n">
+        <f aca="false">SUM(B13:D13)</f>
+        <v>6862.5</v>
+      </c>
+      <c r="F13" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E13/$E$23)</f>
+        <v>0.035667016600855</v>
+      </c>
+      <c r="G13" s="71" t="n">
+        <f aca="false">B13/12</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="70" t="n">
+        <f aca="false">Hypothèses!$B$54*12*(1+Hypothèses!$B$56)^0</f>
+        <v>1800</v>
+      </c>
+      <c r="C14" s="70" t="n">
+        <f aca="false">Hypothèses!$B$54*12*(1+Hypothèses!$B$56)^1</f>
+        <v>2250</v>
+      </c>
+      <c r="D14" s="70" t="n">
+        <f aca="false">Hypothèses!$B$54*12*(1+Hypothèses!$B$56)^2</f>
+        <v>2812.5</v>
+      </c>
+      <c r="E14" s="71" t="n">
+        <f aca="false">SUM(B14:D14)</f>
+        <v>6862.5</v>
+      </c>
+      <c r="F14" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E14/$E$23)</f>
+        <v>0.035667016600855</v>
+      </c>
+      <c r="G14" s="71" t="n">
+        <f aca="false">B14/12</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B16" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$46:$AL$46)</f>
+        <v>7424.5879039242</v>
+      </c>
+      <c r="C16" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$46:$AL$46)</f>
+        <v>25236.3212822042</v>
+      </c>
+      <c r="D16" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$46:$AL$46)</f>
+        <v>50860.5161519019</v>
+      </c>
+      <c r="E16" s="71" t="n">
+        <f aca="false">SUM(B16:D16)</f>
+        <v>83521.4253380303</v>
+      </c>
+      <c r="F16" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E16/$E$23)</f>
+        <v>0.434092541210725</v>
+      </c>
+      <c r="G16" s="71" t="n">
+        <f aca="false">B16/12</f>
+        <v>618.71565866035</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$47:$AL$47)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$47:$AL$47)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$47:$AL$47)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="71" t="n">
+        <f aca="false">SUM(B17:D17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E17/$E$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="71" t="n">
+        <f aca="false">B17/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$48:$AL$48)</f>
+        <v>84.9719742026573</v>
+      </c>
+      <c r="C18" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$48:$AL$48)</f>
+        <v>277.925850252884</v>
+      </c>
+      <c r="D18" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$48:$AL$48)</f>
+        <v>535.942345460035</v>
+      </c>
+      <c r="E18" s="71" t="n">
+        <f aca="false">SUM(B18:D18)</f>
+        <v>898.840169915576</v>
+      </c>
+      <c r="F18" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E18/$E$23)</f>
+        <v>0.00467161344435617</v>
+      </c>
+      <c r="G18" s="71" t="n">
+        <f aca="false">B18/12</f>
+        <v>7.08099785022144</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$49:$AL$49)</f>
+        <v>363.791514242748</v>
+      </c>
+      <c r="C19" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$49:$AL$49)</f>
+        <v>698.480883197636</v>
+      </c>
+      <c r="D19" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$49:$AL$49)</f>
+        <v>1118.29039805302</v>
+      </c>
+      <c r="E19" s="71" t="n">
+        <f aca="false">SUM(B19:D19)</f>
+        <v>2180.56279549341</v>
+      </c>
+      <c r="F19" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E19/$E$23)</f>
+        <v>0.0113332123025239</v>
+      </c>
+      <c r="G19" s="71" t="n">
+        <f aca="false">B19/12</f>
+        <v>30.315959520229</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B20" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$9:$AL$9)*Hypothèses!$B$63</f>
+        <v>853.970690710676</v>
+      </c>
+      <c r="C20" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$9:$AL$9)*Hypothèses!$B$63</f>
+        <v>1639.62648637943</v>
+      </c>
+      <c r="D20" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$9:$AL$9)*Hypothèses!$B$63</f>
+        <v>2625.09483111039</v>
+      </c>
+      <c r="E20" s="71" t="n">
+        <f aca="false">SUM(B20:D20)</f>
+        <v>5118.69200820049</v>
+      </c>
+      <c r="F20" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E20/$E$23)</f>
+        <v>0.0266037847477087</v>
+      </c>
+      <c r="G20" s="71" t="n">
+        <f aca="false">B20/12</f>
+        <v>71.1642242258896</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B21" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$12:$AL$12)*Hypothèses!$B$64</f>
+        <v>569.313793807117</v>
+      </c>
+      <c r="C21" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$12:$AL$12)*Hypothèses!$B$64</f>
+        <v>1093.08432425295</v>
+      </c>
+      <c r="D21" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$12:$AL$12)*Hypothèses!$B$64</f>
+        <v>1750.06322074026</v>
+      </c>
+      <c r="E21" s="71" t="n">
+        <f aca="false">SUM(B21:D21)</f>
+        <v>3412.46133880033</v>
+      </c>
+      <c r="F21" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E21/$E$23)</f>
+        <v>0.0177358564984724</v>
+      </c>
+      <c r="G21" s="71" t="n">
+        <f aca="false">B21/12</f>
+        <v>47.4428161505931</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$14:$AL$14)*Hypothèses!$B$65</f>
+        <v>1138.62758761423</v>
+      </c>
+      <c r="C22" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$14:$AL$14)*Hypothèses!$B$65</f>
+        <v>2186.1686485059</v>
+      </c>
+      <c r="D22" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$14:$AL$14)*Hypothèses!$B$65</f>
+        <v>3500.12644148052</v>
+      </c>
+      <c r="E22" s="71" t="n">
+        <f aca="false">SUM(B22:D22)</f>
+        <v>6824.92267760065</v>
+      </c>
+      <c r="F22" s="72" t="n">
+        <f aca="false">IF($E$23=0,0,E22/$E$23)</f>
+        <v>0.0354717129969449</v>
+      </c>
+      <c r="G22" s="71" t="n">
+        <f aca="false">B22/12</f>
+        <v>94.8856323011862</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="B23" s="44" t="n">
+        <f aca="false">SUM(B6:B14)+SUM(B16:B22)</f>
+        <v>34159.2634645016</v>
+      </c>
+      <c r="C23" s="44" t="n">
+        <f aca="false">SUM(C6:C14)+SUM(C16:C22)</f>
+        <v>60786.607474793</v>
+      </c>
+      <c r="D23" s="44" t="n">
+        <f aca="false">SUM(D6:D14)+SUM(D16:D22)</f>
+        <v>97458.7833887461</v>
+      </c>
+      <c r="E23" s="44" t="n">
+        <f aca="false">SUM(E6:E14)+SUM(E16:E22)</f>
+        <v>192404.654328041</v>
+      </c>
+      <c r="F23" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="44" t="n">
+        <f aca="false">SUM(G6:G14)+SUM(G16:G22)</f>
+        <v>2846.60528870847</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="74" t="s">
+        <v>275</v>
+      </c>
+      <c r="B24" s="75" t="str">
+        <f aca="false">IF(ABS(E23-Synthèse!E30)&lt;1,"OK","Écart")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B27" s="70" t="n">
+        <f aca="false">Hypothèses!$B$69</f>
+        <v>25</v>
+      </c>
+      <c r="E27" s="71" t="n">
+        <f aca="false">B27</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="70" t="n">
+        <f aca="false">Hypothèses!$B$70</f>
+        <v>500</v>
+      </c>
+      <c r="E28" s="71" t="n">
+        <f aca="false">B28</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B29" s="70" t="n">
+        <f aca="false">Hypothèses!$B$71</f>
+        <v>200</v>
+      </c>
+      <c r="E29" s="71" t="n">
+        <f aca="false">B29</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="70" t="n">
+        <f aca="false">Hypothèses!$B$72</f>
+        <v>300</v>
+      </c>
+      <c r="E30" s="71" t="n">
+        <f aca="false">B30</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="B31" s="44" t="n">
+        <f aca="false">SUM(B27:B30)</f>
+        <v>1025</v>
+      </c>
+      <c r="E31" s="44" t="n">
+        <f aca="false">B31</f>
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$42:$AL$42)</f>
+        <v>3299.53867495984</v>
+      </c>
+      <c r="C34" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$42:$AL$42)</f>
+        <v>11259.9308199772</v>
+      </c>
+      <c r="D34" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$42:$AL$42)</f>
+        <v>22888.362682033</v>
+      </c>
+      <c r="E34" s="71" t="n">
+        <f aca="false">SUM(B34:D34)</f>
+        <v>37447.83217697</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$56:$AL$56)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,2,Prévisions!$C$56:$AL$56)</f>
+        <v>3144.32842181068</v>
+      </c>
+      <c r="D35" s="70" t="n">
+        <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,3,Prévisions!$C$56:$AL$56)</f>
+        <v>13678.045012188</v>
+      </c>
+      <c r="E35" s="71" t="n">
+        <f aca="false">SUM(B35:D35)</f>
+        <v>16822.3734339987</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" s="44" t="n">
+        <f aca="false">B23+B31+SUM(B34:B35)</f>
+        <v>38483.8021394615</v>
+      </c>
+      <c r="C38" s="44" t="n">
+        <f aca="false">C23+SUM(C34:C35)</f>
+        <v>75190.866716581</v>
+      </c>
+      <c r="D38" s="44" t="n">
+        <f aca="false">D23+SUM(D34:D35)</f>
+        <v>134025.191082967</v>
+      </c>
+      <c r="E38" s="44" t="n">
+        <f aca="false">E23+E31+SUM(E34:E35)</f>
+        <v>247699.85993901</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="B39" s="70" t="n">
+        <f aca="false">Synthèse!B24</f>
+        <v>20622.116718499</v>
+      </c>
+      <c r="C39" s="70" t="n">
+        <f aca="false">Synthèse!C24</f>
+        <v>70374.5676248577</v>
+      </c>
+      <c r="D39" s="70" t="n">
+        <f aca="false">Synthèse!D24</f>
+        <v>143052.266762706</v>
+      </c>
+      <c r="E39" s="70" t="n">
+        <f aca="false">Synthèse!E24</f>
+        <v>234048.951106063</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="B40" s="76" t="n">
+        <f aca="false">IF(B39=0,0,B23/B39)</f>
+        <v>1.65643827599226</v>
+      </c>
+      <c r="C40" s="76" t="n">
+        <f aca="false">IF(C39=0,0,C23/C39)</f>
+        <v>0.86375816614356</v>
+      </c>
+      <c r="D40" s="76" t="n">
+        <f aca="false">IF(D39=0,0,D23/D39)</f>
+        <v>0.681280944330717</v>
+      </c>
+      <c r="E40" s="76" t="n">
+        <f aca="false">IF(E39=0,0,E23/E39)</f>
+        <v>0.822070141390421</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="77" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="71" t="n">
+        <f aca="false">E10+E11</f>
+        <v>59475</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="B45" s="71" t="n">
+        <f aca="false">SUM(E6:E9)+E18+E19</f>
+        <v>6602.15296540898</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B46" s="71" t="n">
+        <f aca="false">E12+SUM(E20:E22)</f>
+        <v>29081.0760246015</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B47" s="71" t="n">
+        <f aca="false">E16+E17</f>
+        <v>83521.4253380303</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="B48" s="71" t="n">
+        <f aca="false">E13+E14</f>
+        <v>13725</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="B49" s="44" t="n">
+        <f aca="false">SUM(B44:B48)</f>
+        <v>192404.654328041</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FF8EA2F5"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -14211,26 +16339,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="68" t="n">
+        <v>296</v>
+      </c>
+      <c r="B4" s="78" t="n">
         <f aca="false">1+Hypothèses!$B$10*Hypothèses!$B$11</f>
         <v>1.16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -14241,8 +16369,8 @@
       <c r="H6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="69" t="s">
-        <v>262</v>
+      <c r="A7" s="79" t="s">
+        <v>298</v>
       </c>
       <c r="B7" s="64" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$10:$AL$10)</f>
@@ -14251,182 +16379,182 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B8" s="70" t="n">
+        <v>299</v>
+      </c>
+      <c r="B8" s="80" t="n">
         <v>0.4</v>
       </c>
-      <c r="C8" s="70" t="n">
+      <c r="C8" s="80" t="n">
         <v>0.5</v>
       </c>
-      <c r="D8" s="70" t="n">
+      <c r="D8" s="80" t="n">
         <v>0.6</v>
       </c>
-      <c r="E8" s="70" t="n">
+      <c r="E8" s="80" t="n">
         <v>0.7</v>
       </c>
-      <c r="F8" s="70" t="n">
+      <c r="F8" s="80" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="n">
+      <c r="A9" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="72" t="n">
+      <c r="B9" s="71" t="n">
         <f aca="false">$A9*B$8*$B$7/Prix!$B$4</f>
         <v>583.59094192305</v>
       </c>
-      <c r="C9" s="72" t="n">
+      <c r="C9" s="71" t="n">
         <f aca="false">$A9*C$8*$B$7/Prix!$B$4</f>
         <v>729.488677403812</v>
       </c>
-      <c r="D9" s="72" t="n">
+      <c r="D9" s="71" t="n">
         <f aca="false">$A9*D$8*$B$7/Prix!$B$4</f>
         <v>875.386412884575</v>
       </c>
-      <c r="E9" s="72" t="n">
+      <c r="E9" s="71" t="n">
         <f aca="false">$A9*E$8*$B$7/Prix!$B$4</f>
         <v>1021.28414836534</v>
       </c>
-      <c r="F9" s="72" t="n">
+      <c r="F9" s="71" t="n">
         <f aca="false">$A9*F$8*$B$7/Prix!$B$4</f>
         <v>1167.1818838461</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="n">
+      <c r="A10" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="72" t="n">
+      <c r="B10" s="71" t="n">
         <f aca="false">$A10*B$8*$B$7/Prix!$B$4</f>
         <v>1167.1818838461</v>
       </c>
-      <c r="C10" s="72" t="n">
+      <c r="C10" s="71" t="n">
         <f aca="false">$A10*C$8*$B$7/Prix!$B$4</f>
         <v>1458.97735480762</v>
       </c>
-      <c r="D10" s="72" t="n">
+      <c r="D10" s="71" t="n">
         <f aca="false">$A10*D$8*$B$7/Prix!$B$4</f>
         <v>1750.77282576915</v>
       </c>
-      <c r="E10" s="72" t="n">
+      <c r="E10" s="71" t="n">
         <f aca="false">$A10*E$8*$B$7/Prix!$B$4</f>
         <v>2042.56829673067</v>
       </c>
-      <c r="F10" s="72" t="n">
+      <c r="F10" s="71" t="n">
         <f aca="false">$A10*F$8*$B$7/Prix!$B$4</f>
         <v>2334.3637676922</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="n">
+      <c r="A11" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="B11" s="72" t="n">
+      <c r="B11" s="71" t="n">
         <f aca="false">$A11*B$8*$B$7/Prix!$B$4</f>
         <v>1750.77282576915</v>
       </c>
-      <c r="C11" s="72" t="n">
+      <c r="C11" s="71" t="n">
         <f aca="false">$A11*C$8*$B$7/Prix!$B$4</f>
         <v>2188.46603221144</v>
       </c>
-      <c r="D11" s="72" t="n">
+      <c r="D11" s="71" t="n">
         <f aca="false">$A11*D$8*$B$7/Prix!$B$4</f>
         <v>2626.15923865372</v>
       </c>
-      <c r="E11" s="72" t="n">
+      <c r="E11" s="71" t="n">
         <f aca="false">$A11*E$8*$B$7/Prix!$B$4</f>
         <v>3063.85244509601</v>
       </c>
-      <c r="F11" s="72" t="n">
+      <c r="F11" s="71" t="n">
         <f aca="false">$A11*F$8*$B$7/Prix!$B$4</f>
         <v>3501.5456515383</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="n">
+      <c r="A12" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="72" t="n">
+      <c r="B12" s="71" t="n">
         <f aca="false">$A12*B$8*$B$7/Prix!$B$4</f>
         <v>2334.3637676922</v>
       </c>
-      <c r="C12" s="72" t="n">
+      <c r="C12" s="71" t="n">
         <f aca="false">$A12*C$8*$B$7/Prix!$B$4</f>
         <v>2917.95470961525</v>
       </c>
-      <c r="D12" s="72" t="n">
+      <c r="D12" s="71" t="n">
         <f aca="false">$A12*D$8*$B$7/Prix!$B$4</f>
         <v>3501.5456515383</v>
       </c>
-      <c r="E12" s="72" t="n">
+      <c r="E12" s="71" t="n">
         <f aca="false">$A12*E$8*$B$7/Prix!$B$4</f>
         <v>4085.13659346135</v>
       </c>
-      <c r="F12" s="72" t="n">
+      <c r="F12" s="71" t="n">
         <f aca="false">$A12*F$8*$B$7/Prix!$B$4</f>
         <v>4668.7275353844</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="n">
+      <c r="A13" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="B13" s="72" t="n">
+      <c r="B13" s="71" t="n">
         <f aca="false">$A13*B$8*$B$7/Prix!$B$4</f>
         <v>2917.95470961525</v>
       </c>
-      <c r="C13" s="72" t="n">
+      <c r="C13" s="71" t="n">
         <f aca="false">$A13*C$8*$B$7/Prix!$B$4</f>
         <v>3647.44338701906</v>
       </c>
-      <c r="D13" s="72" t="n">
+      <c r="D13" s="71" t="n">
         <f aca="false">$A13*D$8*$B$7/Prix!$B$4</f>
         <v>4376.93206442287</v>
       </c>
-      <c r="E13" s="72" t="n">
+      <c r="E13" s="71" t="n">
         <f aca="false">$A13*E$8*$B$7/Prix!$B$4</f>
         <v>5106.42074182669</v>
       </c>
-      <c r="F13" s="72" t="n">
+      <c r="F13" s="71" t="n">
         <f aca="false">$A13*F$8*$B$7/Prix!$B$4</f>
         <v>5835.9094192305</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="n">
+      <c r="A14" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="B14" s="72" t="n">
+      <c r="B14" s="71" t="n">
         <f aca="false">$A14*B$8*$B$7/Prix!$B$4</f>
         <v>3501.5456515383</v>
       </c>
-      <c r="C14" s="72" t="n">
+      <c r="C14" s="71" t="n">
         <f aca="false">$A14*C$8*$B$7/Prix!$B$4</f>
         <v>4376.93206442287</v>
       </c>
-      <c r="D14" s="72" t="n">
+      <c r="D14" s="71" t="n">
         <f aca="false">$A14*D$8*$B$7/Prix!$B$4</f>
         <v>5252.31847730745</v>
       </c>
-      <c r="E14" s="72" t="n">
+      <c r="E14" s="71" t="n">
         <f aca="false">$A14*E$8*$B$7/Prix!$B$4</f>
         <v>6127.70489019202</v>
       </c>
-      <c r="F14" s="72" t="n">
+      <c r="F14" s="71" t="n">
         <f aca="false">$A14*F$8*$B$7/Prix!$B$4</f>
         <v>7003.0913030766</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -14437,17 +16565,17 @@
       <c r="H17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="69" t="s">
-        <v>266</v>
-      </c>
-      <c r="B18" s="73" t="n">
+      <c r="A18" s="79" t="s">
+        <v>302</v>
+      </c>
+      <c r="B18" s="82" t="n">
         <f aca="false">(1-Hypothèses!$B$31)+Hypothèses!$B$31*(12-Hypothèses!$B$30)/12</f>
         <v>0.95</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>10</v>
@@ -14469,182 +16597,182 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="71" t="n">
+      <c r="A20" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="72" t="n">
+      <c r="B20" s="71" t="n">
         <f aca="false">$A20*B$19*$B$18/Prix!$B$4</f>
         <v>40.948275862069</v>
       </c>
-      <c r="C20" s="72" t="n">
+      <c r="C20" s="71" t="n">
         <f aca="false">$A20*C$19*$B$18/Prix!$B$4</f>
         <v>102.370689655172</v>
       </c>
-      <c r="D20" s="72" t="n">
+      <c r="D20" s="71" t="n">
         <f aca="false">$A20*D$19*$B$18/Prix!$B$4</f>
         <v>204.741379310345</v>
       </c>
-      <c r="E20" s="72" t="n">
+      <c r="E20" s="71" t="n">
         <f aca="false">$A20*E$19*$B$18/Prix!$B$4</f>
         <v>409.48275862069</v>
       </c>
-      <c r="F20" s="72" t="n">
+      <c r="F20" s="71" t="n">
         <f aca="false">$A20*F$19*$B$18/Prix!$B$4</f>
         <v>818.965517241379</v>
       </c>
-      <c r="G20" s="72" t="n">
+      <c r="G20" s="71" t="n">
         <f aca="false">$A20*G$19*$B$18/Prix!$B$4</f>
         <v>2047.41379310345</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="n">
+      <c r="A21" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="72" t="n">
+      <c r="B21" s="71" t="n">
         <f aca="false">$A21*B$19*$B$18/Prix!$B$4</f>
         <v>65.5172413793104</v>
       </c>
-      <c r="C21" s="72" t="n">
+      <c r="C21" s="71" t="n">
         <f aca="false">$A21*C$19*$B$18/Prix!$B$4</f>
         <v>163.793103448276</v>
       </c>
-      <c r="D21" s="72" t="n">
+      <c r="D21" s="71" t="n">
         <f aca="false">$A21*D$19*$B$18/Prix!$B$4</f>
         <v>327.586206896552</v>
       </c>
-      <c r="E21" s="72" t="n">
+      <c r="E21" s="71" t="n">
         <f aca="false">$A21*E$19*$B$18/Prix!$B$4</f>
         <v>655.172413793104</v>
       </c>
-      <c r="F21" s="72" t="n">
+      <c r="F21" s="71" t="n">
         <f aca="false">$A21*F$19*$B$18/Prix!$B$4</f>
         <v>1310.34482758621</v>
       </c>
-      <c r="G21" s="72" t="n">
+      <c r="G21" s="71" t="n">
         <f aca="false">$A21*G$19*$B$18/Prix!$B$4</f>
         <v>3275.86206896552</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71" t="n">
+      <c r="A22" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="72" t="n">
+      <c r="B22" s="71" t="n">
         <f aca="false">$A22*B$19*$B$18/Prix!$B$4</f>
         <v>81.8965517241379</v>
       </c>
-      <c r="C22" s="72" t="n">
+      <c r="C22" s="71" t="n">
         <f aca="false">$A22*C$19*$B$18/Prix!$B$4</f>
         <v>204.741379310345</v>
       </c>
-      <c r="D22" s="72" t="n">
+      <c r="D22" s="71" t="n">
         <f aca="false">$A22*D$19*$B$18/Prix!$B$4</f>
         <v>409.48275862069</v>
       </c>
-      <c r="E22" s="72" t="n">
+      <c r="E22" s="71" t="n">
         <f aca="false">$A22*E$19*$B$18/Prix!$B$4</f>
         <v>818.965517241379</v>
       </c>
-      <c r="F22" s="72" t="n">
+      <c r="F22" s="71" t="n">
         <f aca="false">$A22*F$19*$B$18/Prix!$B$4</f>
         <v>1637.93103448276</v>
       </c>
-      <c r="G22" s="72" t="n">
+      <c r="G22" s="71" t="n">
         <f aca="false">$A22*G$19*$B$18/Prix!$B$4</f>
         <v>4094.8275862069</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="n">
+      <c r="A23" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="72" t="n">
+      <c r="B23" s="71" t="n">
         <f aca="false">$A23*B$19*$B$18/Prix!$B$4</f>
         <v>122.844827586207</v>
       </c>
-      <c r="C23" s="72" t="n">
+      <c r="C23" s="71" t="n">
         <f aca="false">$A23*C$19*$B$18/Prix!$B$4</f>
         <v>307.112068965517</v>
       </c>
-      <c r="D23" s="72" t="n">
+      <c r="D23" s="71" t="n">
         <f aca="false">$A23*D$19*$B$18/Prix!$B$4</f>
         <v>614.224137931035</v>
       </c>
-      <c r="E23" s="72" t="n">
+      <c r="E23" s="71" t="n">
         <f aca="false">$A23*E$19*$B$18/Prix!$B$4</f>
         <v>1228.44827586207</v>
       </c>
-      <c r="F23" s="72" t="n">
+      <c r="F23" s="71" t="n">
         <f aca="false">$A23*F$19*$B$18/Prix!$B$4</f>
         <v>2456.89655172414</v>
       </c>
-      <c r="G23" s="72" t="n">
+      <c r="G23" s="71" t="n">
         <f aca="false">$A23*G$19*$B$18/Prix!$B$4</f>
         <v>6142.24137931035</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71" t="n">
+      <c r="A24" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="72" t="n">
+      <c r="B24" s="71" t="n">
         <f aca="false">$A24*B$19*$B$18/Prix!$B$4</f>
         <v>163.793103448276</v>
       </c>
-      <c r="C24" s="72" t="n">
+      <c r="C24" s="71" t="n">
         <f aca="false">$A24*C$19*$B$18/Prix!$B$4</f>
         <v>409.48275862069</v>
       </c>
-      <c r="D24" s="72" t="n">
+      <c r="D24" s="71" t="n">
         <f aca="false">$A24*D$19*$B$18/Prix!$B$4</f>
         <v>818.965517241379</v>
       </c>
-      <c r="E24" s="72" t="n">
+      <c r="E24" s="71" t="n">
         <f aca="false">$A24*E$19*$B$18/Prix!$B$4</f>
         <v>1637.93103448276</v>
       </c>
-      <c r="F24" s="72" t="n">
+      <c r="F24" s="71" t="n">
         <f aca="false">$A24*F$19*$B$18/Prix!$B$4</f>
         <v>3275.86206896552</v>
       </c>
-      <c r="G24" s="72" t="n">
+      <c r="G24" s="71" t="n">
         <f aca="false">$A24*G$19*$B$18/Prix!$B$4</f>
         <v>8189.65517241379</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="n">
+      <c r="A25" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="B25" s="72" t="n">
+      <c r="B25" s="71" t="n">
         <f aca="false">$A25*B$19*$B$18/Prix!$B$4</f>
         <v>204.741379310345</v>
       </c>
-      <c r="C25" s="72" t="n">
+      <c r="C25" s="71" t="n">
         <f aca="false">$A25*C$19*$B$18/Prix!$B$4</f>
         <v>511.853448275862</v>
       </c>
-      <c r="D25" s="72" t="n">
+      <c r="D25" s="71" t="n">
         <f aca="false">$A25*D$19*$B$18/Prix!$B$4</f>
         <v>1023.70689655172</v>
       </c>
-      <c r="E25" s="72" t="n">
+      <c r="E25" s="71" t="n">
         <f aca="false">$A25*E$19*$B$18/Prix!$B$4</f>
         <v>2047.41379310345</v>
       </c>
-      <c r="F25" s="72" t="n">
+      <c r="F25" s="71" t="n">
         <f aca="false">$A25*F$19*$B$18/Prix!$B$4</f>
         <v>4094.8275862069</v>
       </c>
-      <c r="G25" s="72" t="n">
+      <c r="G25" s="71" t="n">
         <f aca="false">$A25*G$19*$B$18/Prix!$B$4</f>
         <v>10237.0689655172</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -14656,106 +16784,106 @@
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="74" t="n">
+      <c r="A29" s="83" t="n">
         <v>0</v>
       </c>
-      <c r="B29" s="75" t="n">
+      <c r="B29" s="84" t="n">
         <f aca="false">Hypothèses!$B$29*(12-A29)</f>
         <v>120</v>
       </c>
-      <c r="C29" s="76" t="n">
+      <c r="C29" s="72" t="n">
         <f aca="false">A29/12</f>
         <v>0</v>
       </c>
-      <c r="D29" s="75" t="n">
+      <c r="D29" s="84" t="n">
         <f aca="false">B29/12</f>
         <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="74" t="n">
+      <c r="A30" s="83" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="75" t="n">
+      <c r="B30" s="84" t="n">
         <f aca="false">Hypothèses!$B$29*(12-A30)</f>
         <v>110</v>
       </c>
-      <c r="C30" s="76" t="n">
+      <c r="C30" s="72" t="n">
         <f aca="false">A30/12</f>
         <v>0.0833333333333333</v>
       </c>
-      <c r="D30" s="75" t="n">
+      <c r="D30" s="84" t="n">
         <f aca="false">B30/12</f>
         <v>9.16666666666667</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="74" t="n">
+      <c r="A31" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="75" t="n">
+      <c r="B31" s="84" t="n">
         <f aca="false">Hypothèses!$B$29*(12-A31)</f>
         <v>100</v>
       </c>
-      <c r="C31" s="76" t="n">
+      <c r="C31" s="72" t="n">
         <f aca="false">A31/12</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="D31" s="75" t="n">
+      <c r="D31" s="84" t="n">
         <f aca="false">B31/12</f>
         <v>8.33333333333333</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="74" t="n">
+      <c r="A32" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="75" t="n">
+      <c r="B32" s="84" t="n">
         <f aca="false">Hypothèses!$B$29*(12-A32)</f>
         <v>90</v>
       </c>
-      <c r="C32" s="76" t="n">
+      <c r="C32" s="72" t="n">
         <f aca="false">A32/12</f>
         <v>0.25</v>
       </c>
-      <c r="D32" s="75" t="n">
+      <c r="D32" s="84" t="n">
         <f aca="false">B32/12</f>
         <v>7.5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="74" t="n">
+      <c r="A33" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="75" t="n">
+      <c r="B33" s="84" t="n">
         <f aca="false">Hypothèses!$B$29*(12-A33)</f>
         <v>80</v>
       </c>
-      <c r="C33" s="76" t="n">
+      <c r="C33" s="72" t="n">
         <f aca="false">A33/12</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="D33" s="75" t="n">
+      <c r="D33" s="84" t="n">
         <f aca="false">B33/12</f>
         <v>6.66666666666667</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
@@ -14767,99 +16895,99 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="B37" s="75" t="n">
+        <v>314</v>
+      </c>
+      <c r="B37" s="84" t="n">
         <f aca="false">Scénarios!$E$16*(Hypothèses!$B$16+Hypothèses!$B$18*Hypothèses!$B$19)/Prix!$B$4</f>
         <v>8.01724137931035</v>
       </c>
-      <c r="C37" s="75" t="n">
+      <c r="C37" s="84" t="n">
         <f aca="false">Scénarios!$E$16*(Hypothèses!$B$18*Hypothèses!$B$20+Hypothèses!$B$17)</f>
         <v>3.6</v>
       </c>
-      <c r="D37" s="77" t="n">
+      <c r="D37" s="85" t="n">
         <f aca="false">B37-C37</f>
         <v>4.41724137931035</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="B38" s="75" t="n">
+        <v>316</v>
+      </c>
+      <c r="B38" s="84" t="n">
         <f aca="false">(Scénarios!$E$17*(Hypothèses!$B$16+Hypothèses!$B$18*Hypothèses!$B$19)+Hypothèses!$B$27)/Prix!$B$4</f>
         <v>34.3103448275862</v>
       </c>
-      <c r="C38" s="75" t="n">
+      <c r="C38" s="84" t="n">
         <f aca="false">Scénarios!$E$17*(Hypothèses!$B$18*Hypothèses!$B$20+Hypothèses!$B$17)</f>
         <v>9.6</v>
       </c>
-      <c r="D38" s="77" t="n">
+      <c r="D38" s="85" t="n">
         <f aca="false">B38-C38</f>
         <v>24.7103448275862</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="B39" s="75" t="n">
+        <v>318</v>
+      </c>
+      <c r="B39" s="84" t="n">
         <f aca="false">(Hypothèses!$B$29*$B$18+Scénarios!$E$21*Scénarios!$E$22*Scénarios!$E$23*(Hypothèses!$B$16+Hypothèses!$B$18*Hypothèses!$B$19))/Prix!$B$4</f>
         <v>33.8448275862069</v>
       </c>
-      <c r="C39" s="75" t="n">
+      <c r="C39" s="84" t="n">
         <f aca="false">Scénarios!$E$21*Scénarios!$E$22*Scénarios!$E$23*(Hypothèses!$B$18*Hypothèses!$B$20+Hypothèses!$B$17)</f>
         <v>11.52</v>
       </c>
-      <c r="D39" s="77" t="n">
+      <c r="D39" s="85" t="n">
         <f aca="false">B39-C39</f>
         <v>22.3248275862069</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="B40" s="75" t="n">
+        <v>320</v>
+      </c>
+      <c r="B40" s="84" t="n">
         <f aca="false">(Hypothèses!$B$32/Hypothèses!$B$8+Hypothèses!$B$22*Hypothèses!$B$21)/Prix!$B$4</f>
         <v>1.5124016938899</v>
       </c>
-      <c r="C40" s="75" t="n">
+      <c r="C40" s="84" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="D40" s="77" t="n">
+      <c r="D40" s="85" t="n">
         <f aca="false">B40-C40</f>
         <v>1.5124016938899</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -14888,7 +17016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF8EA2F5"/>
@@ -14903,17 +17031,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -14923,52 +17051,52 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="78" t="n">
+        <v>325</v>
+      </c>
+      <c r="B5" s="86" t="n">
         <f aca="false">Hypothèses!$B$16/Prix!$B$4</f>
         <v>0.021551724137931</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="B6" s="78" t="n">
+        <v>326</v>
+      </c>
+      <c r="B6" s="86" t="n">
         <f aca="false">Hypothèses!$B$18*Hypothèses!$B$19/Prix!$B$4</f>
         <v>0.00517241379310345</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="B7" s="78" t="n">
+        <v>327</v>
+      </c>
+      <c r="B7" s="86" t="n">
         <f aca="false">Hypothèses!$B$18*Hypothèses!$B$20+Hypothèses!$B$17</f>
         <v>0.012</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="B8" s="79" t="n">
+        <v>328</v>
+      </c>
+      <c r="B8" s="87" t="n">
         <f aca="false">B5+B6-B7</f>
         <v>0.0147241379310345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="B9" s="75" t="n">
+        <v>329</v>
+      </c>
+      <c r="B9" s="84" t="n">
         <f aca="false">B8*Hypothèses!$B$23</f>
         <v>0.29448275862069</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -14978,34 +17106,34 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="B12" s="80" t="n">
+        <v>331</v>
+      </c>
+      <c r="B12" s="70" t="n">
         <f aca="false">Hypothèses!$B$55</f>
         <v>1977</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="B13" s="80" t="n">
+        <v>332</v>
+      </c>
+      <c r="B13" s="70" t="n">
         <f aca="false">(SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$38:$AL$38)+SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$39:$AL$39)+SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$40:$AL$40))/12/Prix!$B$4</f>
         <v>289.652731684797</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="B14" s="72" t="n">
+        <v>333</v>
+      </c>
+      <c r="B14" s="71" t="n">
         <f aca="false">MAX(0,B12-B13)</f>
         <v>1687.3472683152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="38" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="B15" s="65" t="n">
         <f aca="false">IF(B8&lt;=0,"Impossible : la contribution par $ est négative",B14/B8)</f>
@@ -15014,27 +17142,27 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B16" s="81" t="n">
+        <v>335</v>
+      </c>
+      <c r="B16" s="88" t="n">
         <f aca="false">IF(ISNUMBER(B15),B15/Hypothèses!$B$23,"-")</f>
         <v>5729.86777296732</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="B17" s="82" t="n">
+        <v>336</v>
+      </c>
+      <c r="B17" s="89" t="n">
         <f aca="false">IF(ISNUMBER(B15),B15/Scénarios!$E$16,"-")</f>
         <v>381.991184864488</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="B18" s="82" t="n">
+        <v>337</v>
+      </c>
+      <c r="B18" s="89" t="n">
         <f aca="false">IF(Prix!$D$38&lt;=0,"-",B12/Prix!$D$38)</f>
         <v>80.0069773932459</v>
       </c>
@@ -15052,61 +17180,61 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="B21" s="80" t="n">
+        <v>338</v>
+      </c>
+      <c r="B21" s="70" t="n">
         <f aca="false">Hypothèses!$B$77*Hypothèses!$B$9</f>
         <v>1270</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="B22" s="72" t="n">
+        <v>339</v>
+      </c>
+      <c r="B22" s="71" t="n">
         <f aca="false">B21/(1-Hypothèses!$B$12)</f>
         <v>1814.28571428571</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="B23" s="83" t="n">
+        <v>334</v>
+      </c>
+      <c r="B23" s="90" t="n">
         <f aca="false">IF(B8&lt;=0,"Impossible",(B22+B14)/B8)</f>
         <v>237815.823174301</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B24" s="84" t="n">
+        <v>335</v>
+      </c>
+      <c r="B24" s="91" t="n">
         <f aca="false">IF(ISNUMBER(B23),B23/Hypothèses!$B$23,"-")</f>
         <v>11890.7911587151</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="B25" s="81" t="n">
+        <v>340</v>
+      </c>
+      <c r="B25" s="88" t="n">
         <f aca="false">IF(ISNUMBER(B24),B24/30,"-")</f>
         <v>396.359705290502</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="B26" s="81" t="n">
+        <v>336</v>
+      </c>
+      <c r="B26" s="88" t="n">
         <f aca="false">IF(ISNUMBER(B23),B23/Scénarios!$E$16,"-")</f>
         <v>792.719410581004</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="B27" s="63" t="str">
         <f aca="false">IF(MIN(Prévisions!$C$62:$AL$62)=999,"Pas en 3 ans","Mois "&amp;MIN(Prévisions!$C$62:$AL$62))</f>
@@ -15115,7 +17243,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -15125,173 +17253,173 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="B30" s="85" t="n">
+        <v>343</v>
+      </c>
+      <c r="B30" s="92" t="n">
         <v>500</v>
       </c>
-      <c r="D30" s="86" t="s">
-        <v>308</v>
-      </c>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
+      <c r="D30" s="93" t="s">
+        <v>344</v>
+      </c>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B31" s="87" t="n">
+        <v>345</v>
+      </c>
+      <c r="B31" s="94" t="n">
         <v>20</v>
       </c>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B32" s="36" t="n">
         <f aca="false">Hypothèses!$B$16</f>
         <v>0.025</v>
       </c>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="B33" s="77" t="n">
+        <v>346</v>
+      </c>
+      <c r="B33" s="85" t="n">
         <f aca="false">B30*B31*B32/Prix!$B$4</f>
         <v>215.51724137931</v>
       </c>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>275</v>
-      </c>
       <c r="C35" s="21" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="74" t="n">
+      <c r="A36" s="83" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="72" t="n">
+      <c r="B36" s="71" t="n">
         <f aca="false">A36*$B$33</f>
         <v>215.51724137931</v>
       </c>
-      <c r="C36" s="72" t="n">
+      <c r="C36" s="71" t="n">
         <f aca="false">B36*12</f>
         <v>2586.20689655172</v>
       </c>
-      <c r="D36" s="76" t="n">
+      <c r="D36" s="72" t="n">
         <f aca="false">IF($B$12=0,0,B36/$B$12)</f>
         <v>0.109012261699196</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="74" t="n">
+      <c r="A37" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="72" t="n">
+      <c r="B37" s="71" t="n">
         <f aca="false">A37*$B$33</f>
         <v>431.034482758621</v>
       </c>
-      <c r="C37" s="72" t="n">
+      <c r="C37" s="71" t="n">
         <f aca="false">B37*12</f>
         <v>5172.41379310345</v>
       </c>
-      <c r="D37" s="76" t="n">
+      <c r="D37" s="72" t="n">
         <f aca="false">IF($B$12=0,0,B37/$B$12)</f>
         <v>0.218024523398392</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="74" t="n">
+      <c r="A38" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="72" t="n">
+      <c r="B38" s="71" t="n">
         <f aca="false">A38*$B$33</f>
         <v>862.068965517241</v>
       </c>
-      <c r="C38" s="72" t="n">
+      <c r="C38" s="71" t="n">
         <f aca="false">B38*12</f>
         <v>10344.8275862069</v>
       </c>
-      <c r="D38" s="76" t="n">
+      <c r="D38" s="72" t="n">
         <f aca="false">IF($B$12=0,0,B38/$B$12)</f>
         <v>0.436049046796784</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="74" t="n">
+      <c r="A39" s="83" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="72" t="n">
+      <c r="B39" s="71" t="n">
         <f aca="false">A39*$B$33</f>
         <v>1293.10344827586</v>
       </c>
-      <c r="C39" s="72" t="n">
+      <c r="C39" s="71" t="n">
         <f aca="false">B39*12</f>
         <v>15517.2413793103</v>
       </c>
-      <c r="D39" s="76" t="n">
+      <c r="D39" s="72" t="n">
         <f aca="false">IF($B$12=0,0,B39/$B$12)</f>
         <v>0.654073570195176</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="74" t="n">
+      <c r="A40" s="83" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="72" t="n">
+      <c r="B40" s="71" t="n">
         <f aca="false">A40*$B$33</f>
         <v>1724.13793103448</v>
       </c>
-      <c r="C40" s="72" t="n">
+      <c r="C40" s="71" t="n">
         <f aca="false">B40*12</f>
         <v>20689.6551724138</v>
       </c>
-      <c r="D40" s="76" t="n">
+      <c r="D40" s="72" t="n">
         <f aca="false">IF($B$12=0,0,B40/$B$12)</f>
         <v>0.872098093593567</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="74" t="n">
+      <c r="A41" s="83" t="n">
         <v>10</v>
       </c>
-      <c r="B41" s="72" t="n">
+      <c r="B41" s="71" t="n">
         <f aca="false">A41*$B$33</f>
         <v>2155.1724137931</v>
       </c>
-      <c r="C41" s="72" t="n">
+      <c r="C41" s="71" t="n">
         <f aca="false">B41*12</f>
         <v>25862.0689655172</v>
       </c>
-      <c r="D41" s="76" t="n">
+      <c r="D41" s="72" t="n">
         <f aca="false">IF($B$12=0,0,B41/$B$12)</f>
         <v>1.09012261699196</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="B43" s="84" t="n">
+        <v>350</v>
+      </c>
+      <c r="B43" s="91" t="n">
         <f aca="false">IF(B31*B32=0,"-",B12*Prix!$B$4/(B31*B32))</f>
         <v>4586.64</v>
       </c>
@@ -15315,7 +17443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF8EA2F5"/>
@@ -15330,26 +17458,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="B4" s="80" t="n">
+        <v>353</v>
+      </c>
+      <c r="B4" s="70" t="n">
         <f aca="false">SUMIF(Prévisions!$C$5:$AL$5,1,Prévisions!$C$28:$AL$28)/12</f>
         <v>30935.7829330175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="B5" s="36" t="n">
         <f aca="false">Hypothèses!$B$20</f>
@@ -15358,7 +17486,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="B6" s="36" t="n">
         <f aca="false">Hypothèses!$B$19</f>
@@ -15367,41 +17495,41 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="88" t="n">
+      <c r="A9" s="95" t="n">
         <v>0.01</v>
       </c>
-      <c r="B9" s="75" t="n">
+      <c r="B9" s="84" t="n">
         <f aca="false">100*A9/Prix!$B$4</f>
         <v>0.862068965517241</v>
       </c>
-      <c r="C9" s="75" t="n">
+      <c r="C9" s="84" t="n">
         <f aca="false">100*$B$5</f>
         <v>2</v>
       </c>
-      <c r="D9" s="77" t="n">
+      <c r="D9" s="85" t="n">
         <f aca="false">B9-C9</f>
         <v>-1.13793103448276</v>
       </c>
-      <c r="E9" s="72" t="n">
+      <c r="E9" s="71" t="n">
         <f aca="false">$B$4/100*D9</f>
         <v>-352.027874755027</v>
       </c>
@@ -15411,22 +17539,22 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="88" t="n">
+      <c r="A10" s="95" t="n">
         <v>0.015</v>
       </c>
-      <c r="B10" s="75" t="n">
+      <c r="B10" s="84" t="n">
         <f aca="false">100*A10/Prix!$B$4</f>
         <v>1.29310344827586</v>
       </c>
-      <c r="C10" s="75" t="n">
+      <c r="C10" s="84" t="n">
         <f aca="false">100*$B$5</f>
         <v>2</v>
       </c>
-      <c r="D10" s="77" t="n">
+      <c r="D10" s="85" t="n">
         <f aca="false">B10-C10</f>
         <v>-0.706896551724138</v>
       </c>
-      <c r="E10" s="72" t="n">
+      <c r="E10" s="71" t="n">
         <f aca="false">$B$4/100*D10</f>
         <v>-218.683982802365</v>
       </c>
@@ -15436,22 +17564,22 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="88" t="n">
+      <c r="A11" s="95" t="n">
         <v>0.02</v>
       </c>
-      <c r="B11" s="75" t="n">
+      <c r="B11" s="84" t="n">
         <f aca="false">100*A11/Prix!$B$4</f>
         <v>1.72413793103448</v>
       </c>
-      <c r="C11" s="75" t="n">
+      <c r="C11" s="84" t="n">
         <f aca="false">100*$B$5</f>
         <v>2</v>
       </c>
-      <c r="D11" s="77" t="n">
+      <c r="D11" s="85" t="n">
         <f aca="false">B11-C11</f>
         <v>-0.275862068965517</v>
       </c>
-      <c r="E11" s="72" t="n">
+      <c r="E11" s="71" t="n">
         <f aca="false">$B$4/100*D11</f>
         <v>-85.3400908497034</v>
       </c>
@@ -15461,22 +17589,22 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="88" t="n">
+      <c r="A12" s="95" t="n">
         <v>0.025</v>
       </c>
-      <c r="B12" s="75" t="n">
+      <c r="B12" s="84" t="n">
         <f aca="false">100*A12/Prix!$B$4</f>
         <v>2.1551724137931</v>
       </c>
-      <c r="C12" s="75" t="n">
+      <c r="C12" s="84" t="n">
         <f aca="false">100*$B$5</f>
         <v>2</v>
       </c>
-      <c r="D12" s="77" t="n">
+      <c r="D12" s="85" t="n">
         <f aca="false">B12-C12</f>
         <v>0.155172413793104</v>
       </c>
-      <c r="E12" s="72" t="n">
+      <c r="E12" s="71" t="n">
         <f aca="false">$B$4/100*D12</f>
         <v>48.0038011029583</v>
       </c>
@@ -15486,22 +17614,22 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="88" t="n">
+      <c r="A13" s="95" t="n">
         <v>0.03</v>
       </c>
-      <c r="B13" s="75" t="n">
+      <c r="B13" s="84" t="n">
         <f aca="false">100*A13/Prix!$B$4</f>
         <v>2.58620689655172</v>
       </c>
-      <c r="C13" s="75" t="n">
+      <c r="C13" s="84" t="n">
         <f aca="false">100*$B$5</f>
         <v>2</v>
       </c>
-      <c r="D13" s="77" t="n">
+      <c r="D13" s="85" t="n">
         <f aca="false">B13-C13</f>
         <v>0.586206896551724</v>
       </c>
-      <c r="E13" s="72" t="n">
+      <c r="E13" s="71" t="n">
         <f aca="false">$B$4/100*D13</f>
         <v>181.34769305562</v>
       </c>
@@ -15511,22 +17639,22 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="88" t="n">
+      <c r="A14" s="95" t="n">
         <v>0.035</v>
       </c>
-      <c r="B14" s="75" t="n">
+      <c r="B14" s="84" t="n">
         <f aca="false">100*A14/Prix!$B$4</f>
         <v>3.01724137931035</v>
       </c>
-      <c r="C14" s="75" t="n">
+      <c r="C14" s="84" t="n">
         <f aca="false">100*$B$5</f>
         <v>2</v>
       </c>
-      <c r="D14" s="77" t="n">
+      <c r="D14" s="85" t="n">
         <f aca="false">B14-C14</f>
         <v>1.01724137931035</v>
       </c>
-      <c r="E14" s="72" t="n">
+      <c r="E14" s="71" t="n">
         <f aca="false">$B$4/100*D14</f>
         <v>314.691585008282</v>
       </c>
@@ -15536,22 +17664,22 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="88" t="n">
+      <c r="A15" s="95" t="n">
         <v>0.04</v>
       </c>
-      <c r="B15" s="75" t="n">
+      <c r="B15" s="84" t="n">
         <f aca="false">100*A15/Prix!$B$4</f>
         <v>3.44827586206897</v>
       </c>
-      <c r="C15" s="75" t="n">
+      <c r="C15" s="84" t="n">
         <f aca="false">100*$B$5</f>
         <v>2</v>
       </c>
-      <c r="D15" s="77" t="n">
+      <c r="D15" s="85" t="n">
         <f aca="false">B15-C15</f>
         <v>1.44827586206897</v>
       </c>
-      <c r="E15" s="72" t="n">
+      <c r="E15" s="71" t="n">
         <f aca="false">$B$4/100*D15</f>
         <v>448.035476960943</v>
       </c>
@@ -15562,7 +17690,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -15587,284 +17715,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF8EA2F5"/>
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="B4" s="80" t="n">
-        <f aca="false">INDEX(Prévisions!$C$55:$AL$55,12)</f>
-        <v>-228.255271613358</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B5" s="80" t="n">
-        <f aca="false">INDEX(Prévisions!$C$21:$AL$21,12)+INDEX(Prévisions!$C$22:$AL$22,12)+INDEX(Prévisions!$C$27:$AL$27,12)</f>
-        <v>104412.27435579</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="B6" s="36" t="n">
-        <f aca="false">Hypothèses!$B$16</f>
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="B7" s="78" t="n">
-        <f aca="false">Hypothèses!$B$18*(Hypothèses!$B$19/Prix!$B$4-Hypothèses!$B$20)</f>
-        <v>-0.00682758620689655</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="B9" s="89" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C9" s="89" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D9" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="89" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F9" s="89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="89" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="88" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B10" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A10/Prix!$B$4+$B$7)</f>
-        <v>-1672.02499632617</v>
-      </c>
-      <c r="C10" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A10/Prix!$B$4+$B$7)</f>
-        <v>-1625.21949402875</v>
-      </c>
-      <c r="D10" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A10/Prix!$B$4+$B$7)</f>
-        <v>-1578.41399173133</v>
-      </c>
-      <c r="E10" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A10/Prix!$B$4+$B$7)</f>
-        <v>-1484.80298713648</v>
-      </c>
-      <c r="F10" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A10/Prix!$B$4+$B$7)</f>
-        <v>-1391.19198254163</v>
-      </c>
-      <c r="G10" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A10/Prix!$B$4+$B$7)</f>
-        <v>-1203.96997335194</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="88" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="B11" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A11/Prix!$B$4+$B$7)</f>
-        <v>-1446.99854297318</v>
-      </c>
-      <c r="C11" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A11/Prix!$B$4+$B$7)</f>
-        <v>-1287.67981399926</v>
-      </c>
-      <c r="D11" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A11/Prix!$B$4+$B$7)</f>
-        <v>-1128.36108502534</v>
-      </c>
-      <c r="E11" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A11/Prix!$B$4+$B$7)</f>
-        <v>-809.723627077496</v>
-      </c>
-      <c r="F11" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A11/Prix!$B$4+$B$7)</f>
-        <v>-491.086169129656</v>
-      </c>
-      <c r="G11" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A11/Prix!$B$4+$B$7)</f>
-        <v>146.188746766026</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="88" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="B12" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A12/Prix!$B$4+$B$7)</f>
-        <v>-1221.97208962018</v>
-      </c>
-      <c r="C12" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A12/Prix!$B$4+$B$7)</f>
-        <v>-950.140133969765</v>
-      </c>
-      <c r="D12" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A12/Prix!$B$4+$B$7)</f>
-        <v>-678.308178319347</v>
-      </c>
-      <c r="E12" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A12/Prix!$B$4+$B$7)</f>
-        <v>-134.644267018512</v>
-      </c>
-      <c r="F12" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A12/Prix!$B$4+$B$7)</f>
-        <v>409.019644282324</v>
-      </c>
-      <c r="G12" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A12/Prix!$B$4+$B$7)</f>
-        <v>1496.34746688399</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="88" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="B13" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A13/Prix!$B$4+$B$7)</f>
-        <v>-996.945636267188</v>
-      </c>
-      <c r="C13" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A13/Prix!$B$4+$B$7)</f>
-        <v>-612.600453940273</v>
-      </c>
-      <c r="D13" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A13/Prix!$B$4+$B$7)</f>
-        <v>-228.255271613358</v>
-      </c>
-      <c r="E13" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A13/Prix!$B$4+$B$7)</f>
-        <v>540.435093040472</v>
-      </c>
-      <c r="F13" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A13/Prix!$B$4+$B$7)</f>
-        <v>1309.1254576943</v>
-      </c>
-      <c r="G13" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A13/Prix!$B$4+$B$7)</f>
-        <v>2846.50618700196</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="88" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="B14" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A14/Prix!$B$4+$B$7)</f>
-        <v>-771.919182914193</v>
-      </c>
-      <c r="C14" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A14/Prix!$B$4+$B$7)</f>
-        <v>-275.060773910781</v>
-      </c>
-      <c r="D14" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A14/Prix!$B$4+$B$7)</f>
-        <v>221.797635092631</v>
-      </c>
-      <c r="E14" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A14/Prix!$B$4+$B$7)</f>
-        <v>1215.51445309946</v>
-      </c>
-      <c r="F14" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A14/Prix!$B$4+$B$7)</f>
-        <v>2209.23127110628</v>
-      </c>
-      <c r="G14" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A14/Prix!$B$4+$B$7)</f>
-        <v>4196.66490711993</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="88" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="B15" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*B$9*($A15/Prix!$B$4+$B$7)</f>
-        <v>-546.892729561198</v>
-      </c>
-      <c r="C15" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*C$9*($A15/Prix!$B$4+$B$7)</f>
-        <v>62.4789061187116</v>
-      </c>
-      <c r="D15" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*D$9*($A15/Prix!$B$4+$B$7)</f>
-        <v>671.850541798621</v>
-      </c>
-      <c r="E15" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*E$9*($A15/Prix!$B$4+$B$7)</f>
-        <v>1890.59381315844</v>
-      </c>
-      <c r="F15" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*F$9*($A15/Prix!$B$4+$B$7)</f>
-        <v>3109.33708451826</v>
-      </c>
-      <c r="G15" s="72" t="n">
-        <f aca="false">$B$4-$B$5*($B$6/Prix!$B$4+$B$7)+$B$5*G$9*($A15/Prix!$B$4+$B$7)</f>
-        <v>5546.8236272379</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>333</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B10:G15">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>